--- a/Hand_edited_log/1/student/cuongnvhe181200/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/cuongnvhe181200/TC1/GradeDetail.xlsx
@@ -1038,10 +1038,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>49678</x:v>
+        <x:v>50164</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1094,10 +1094,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>49678</x:v>
+        <x:v>50164</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,10 +1150,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>49678</x:v>
+        <x:v>50164</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
         <x:v>52</x:v>
@@ -1206,10 +1206,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>49678</x:v>
+        <x:v>50164</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1262,10 +1262,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>49678</x:v>
+        <x:v>50164</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>52</x:v>
@@ -1318,10 +1318,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>49678</x:v>
+        <x:v>50164</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>52</x:v>
@@ -1374,10 +1374,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>49678</x:v>
+        <x:v>50164</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1430,10 +1430,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>49678</x:v>
+        <x:v>50164</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>52</x:v>
@@ -1486,10 +1486,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>49678</x:v>
+        <x:v>50164</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>
